--- a/data/processed/apple_analysis.xlsx
+++ b/data/processed/apple_analysis.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="825" yWindow="2017" windowWidth="11872" windowHeight="9308" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ratios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Charts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -52,7 +52,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -124,6 +124,2545 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Revenue</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$2:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+                <pt idx="1">
+                  <v>383285</v>
+                </pt>
+                <pt idx="2">
+                  <v>391035</v>
+                </pt>
+                <pt idx="3">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Net Income</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$2:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+                <pt idx="1">
+                  <v>96995</v>
+                </pt>
+                <pt idx="2">
+                  <v>93736</v>
+                </pt>
+                <pt idx="3">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>None</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Amount in USD(Billions)</a:t>
+                </a:r>
+              </a:p>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>None</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800"/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Revenue</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$2:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+                <pt idx="1">
+                  <v>383285</v>
+                </pt>
+                <pt idx="2">
+                  <v>391035</v>
+                </pt>
+                <pt idx="3">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Net Income</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$2:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+                <pt idx="1">
+                  <v>96995</v>
+                </pt>
+                <pt idx="2">
+                  <v>93736</v>
+                </pt>
+                <pt idx="3">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD (Millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD (Millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD (Millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$3:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>383285</v>
+                </pt>
+                <pt idx="1">
+                  <v>391035</v>
+                </pt>
+                <pt idx="2">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$2</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$3:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>96995</v>
+                </pt>
+                <pt idx="1">
+                  <v>93736</v>
+                </pt>
+                <pt idx="2">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>USD (Millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000"/>
+              <a:t>Revenue and Net Income over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="1"/>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1573315277777778"/>
+          <y val="0.1516944444444444"/>
+          <w val="0.5766666666666668"/>
+          <h val="0.6119444444444444"/>
+        </manualLayout>
+      </layout>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Charts!$O$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Revenue</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <delete val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$O$2:$O$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>394328</v>
+                </pt>
+                <pt idx="1">
+                  <v>383285</v>
+                </pt>
+                <pt idx="2">
+                  <v>391035</v>
+                </pt>
+                <pt idx="3">
+                  <v>416161</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Charts!$P$1</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Net Income</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>Charts!$N$2:$N$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>2022</v>
+                </pt>
+                <pt idx="1">
+                  <v>2023</v>
+                </pt>
+                <pt idx="2">
+                  <v>2024</v>
+                </pt>
+                <pt idx="3">
+                  <v>2025</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Charts!$P$2:$P$5</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="4"/>
+                <pt idx="0">
+                  <v>99803</v>
+                </pt>
+                <pt idx="1">
+                  <v>96995</v>
+                </pt>
+                <pt idx="2">
+                  <v>93736</v>
+                </pt>
+                <pt idx="3">
+                  <v>112010</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="1"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="1417795440"/>
+        <axId val="1412871856"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1600"/>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="1"/>
+        </title>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="in"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+      <catAx>
+        <axId val="1417795440"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="1412871856"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
+      </catAx>
+      <valAx>
+        <axId val="1412871856"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="r"/>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="1417795440"/>
+        <crosses val="max"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="1"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:alpha val="99000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,7 +2970,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -559,4 +3098,80 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="N1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="N2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="O2" t="n">
+        <v>394328</v>
+      </c>
+      <c r="P2" t="n">
+        <v>99803</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="N3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="O3" t="n">
+        <v>383285</v>
+      </c>
+      <c r="P3" t="n">
+        <v>96995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="N4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="O4" t="n">
+        <v>391035</v>
+      </c>
+      <c r="P4" t="n">
+        <v>93736</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="N5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O5" t="n">
+        <v>416161</v>
+      </c>
+      <c r="P5" t="n">
+        <v>112010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>